--- a/Results/idealista_2026-03-03.xlsx
+++ b/Results/idealista_2026-03-03.xlsx
@@ -1501,24 +1501,24 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>28min via Metro M4
-🚶 4min walk → Frattini
+          <t>26min via Metro M4
+🚶 3min walk → Frattini
 🚇 Metro M4 (10 stops): Frattini -&gt; San Babila
 🚶 10min walk → P.za del Duomo</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>28min via Metro M4
-🚶 4min walk → Frattini
+          <t>26min via Metro M4
+🚶 3min walk → Frattini
 🚇 Metro M4 (11 stops): Frattini -&gt; Tricolore
 🚶 8min walk → Istituto dei ciechi di milano, Via Vivaio, 7, 20122 Milano MI</t>
         </is>
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t>31min via Metro M4 → Metro 2
-🚶 4min walk → Frattini
+          <t>28min via Metro M4 → Metro 2
+🚶 3min walk → Frattini
 🚇 Metro M4 (5 stops): Frattini -&gt; S. Ambrogio
 🚶 1min walk → S.Ambrogio
 🚇 Metro 2 (3 stops): S.Ambrogio -&gt; Romolo
@@ -1527,8 +1527,8 @@
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>82min via Metro M4 → Metro 2 → Heavy_Rail RE 51
-🚶 4min walk → Frattini
+          <t>80min via Metro M4 → Metro 2 → Heavy_Rail RE 51
+🚶 3min walk → Frattini
 🚇 Metro M4 (5 stops): Frattini -&gt; S. Ambrogio
 🚶 1min walk → S.Ambrogio
 🚇 Metro 2 (4 stops): S.Ambrogio -&gt; Garibaldi FS
